--- a/derivatives/BAR/P5425_preprocessed.xlsx
+++ b/derivatives/BAR/P5425_preprocessed.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>listno</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>trialno</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>conceptno</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>concept</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>concept_HU</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>duration</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>responded</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>response</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>response_HU</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>similarity</t>
         </is>
@@ -747,7 +759,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.4084874093532562</v>
+        <v>0.4084874391555786</v>
       </c>
     </row>
     <row r="8">
@@ -1207,7 +1219,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0.106252484023571</v>
+        <v>0.1062524914741516</v>
       </c>
     </row>
     <row r="18">
@@ -1301,7 +1313,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0.1047540828585625</v>
+        <v>0.1047540754079819</v>
       </c>
     </row>
     <row r="20">
@@ -1489,7 +1501,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0.09236016869544983</v>
+        <v>0.09236017614603043</v>
       </c>
     </row>
     <row r="24">
@@ -1541,7 +1553,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0.1501886248588562</v>
+        <v>0.1501886397600174</v>
       </c>
     </row>
     <row r="25">
@@ -1771,7 +1783,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.2455641478300095</v>
+        <v>0.2455641329288483</v>
       </c>
     </row>
     <row r="30">
@@ -1949,7 +1961,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.4480665922164917</v>
+        <v>0.4480665624141693</v>
       </c>
     </row>
     <row r="34">
@@ -2053,7 +2065,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0.2673603594303131</v>
+        <v>0.2673603892326355</v>
       </c>
     </row>
     <row r="36">
@@ -2105,7 +2117,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0.7498184442520142</v>
+        <v>0.7498183846473694</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2169,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0.1929962188005447</v>
+        <v>0.1929962337017059</v>
       </c>
     </row>
     <row r="38">
@@ -2209,7 +2221,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.4482640624046326</v>
+        <v>0.4482640326023102</v>
       </c>
     </row>
     <row r="39">
@@ -2261,7 +2273,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0.4480665922164917</v>
+        <v>0.4480665624141693</v>
       </c>
     </row>
     <row r="40">
@@ -2825,7 +2837,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.509489119052887</v>
+        <v>0.5094890594482422</v>
       </c>
     </row>
     <row r="52">
